--- a/esyluban/examples/release/DataTables/test/luban_assistant_test_multi_rows.xlsx
+++ b/esyluban/examples/release/DataTables/test/luban_assistant_test_multi_rows.xlsx
@@ -715,8 +715,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="D1:I1"/>
+    <mergeCell ref="D2:I2"/>
+    <mergeCell ref="G3:H3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
